--- a/practice/answers/s1_q11.xlsx
+++ b/practice/answers/s1_q11.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Answer" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Answer" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,7 +21,7 @@
     <numFmt numFmtId="165" formatCode="0.0"/>
     <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,45 +30,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Arial"/>
       <b val="1"/>
-      <color rgb="004A7C59"/>
-      <sz val="13"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="005C6B62"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="0024302A"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="0024302A"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Consolas"/>
-      <color rgb="002F5D46"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="005C6B62"/>
-      <sz val="9"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -77,7 +42,27 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F6EFD9"/>
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F4CCCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9EAD3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00CFE2F3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9D2E9"/>
       </patternFill>
     </fill>
   </fills>
@@ -93,31 +78,30 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -483,182 +467,315 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>A grid from one formula</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="32" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Crops down, grades across, one formula filled both ways. The crop reference locks its column, the grade factor locks its row, the price locks both.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="18" customHeight="1"/>
-    <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
+    <row r="1">
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Grade</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>No. 1</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>No. 2</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>0.93</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>Base price ($/bu)</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n">
+      <c r="B4" s="3" t="n">
         <v>14.2</v>
       </c>
-    </row>
-    <row r="5" ht="18" customHeight="1"/>
-    <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Sample</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>0.78</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>Revenue ($/ac)</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>No. 1</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>No. 2</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Crop</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="inlineStr">
         <is>
           <t>Yield (bu/ac)</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>No. 1</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>No. 2</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>Sample</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="C7" s="6" t="n">
+      <c r="C7" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="D7" s="6" t="n">
+      <c r="D7" s="5" t="n">
         <v>0.93</v>
       </c>
-      <c r="E7" s="6" t="n">
+      <c r="E7" s="5" t="n">
         <v>0.78</v>
       </c>
     </row>
-    <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Canola</t>
         </is>
       </c>
-      <c r="B8" s="8" t="n">
+      <c r="B8" s="6" t="n">
         <v>41.2</v>
       </c>
-      <c r="C8" s="9">
+      <c r="C8" s="7">
         <f>$B8*$B$4*C$7</f>
         <v/>
       </c>
-      <c r="D8" s="9">
+      <c r="D8" s="7">
         <f>$B8*$B$4*D$7</f>
         <v/>
       </c>
-      <c r="E8" s="9">
+      <c r="E8" s="7">
         <f>$B8*$B$4*E$7</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>Wheat</t>
         </is>
       </c>
-      <c r="B9" s="8" t="n">
+      <c r="B9" s="6" t="n">
         <v>58.6</v>
       </c>
-      <c r="C9" s="9">
+      <c r="C9" s="7">
         <f>$B9*$B$4*C$7</f>
         <v/>
       </c>
-      <c r="D9" s="9">
+      <c r="D9" s="7">
         <f>$B9*$B$4*D$7</f>
         <v/>
       </c>
-      <c r="E9" s="9">
+      <c r="E9" s="7">
         <f>$B9*$B$4*E$7</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>Barley</t>
         </is>
       </c>
-      <c r="B10" s="8" t="n">
+      <c r="B10" s="6" t="n">
         <v>72.40000000000001</v>
       </c>
-      <c r="C10" s="9">
+      <c r="C10" s="7">
         <f>$B10*$B$4*C$7</f>
         <v/>
       </c>
-      <c r="D10" s="9">
+      <c r="D10" s="7">
         <f>$B10*$B$4*D$7</f>
         <v/>
       </c>
-      <c r="E10" s="9">
+      <c r="E10" s="7">
         <f>$B10*$B$4*E$7</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="18" customHeight="1"/>
-    <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>The one formula</t>
-        </is>
-      </c>
-      <c r="C12" s="10">
-        <f>_xlfn.FORMULATEXT(C8)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="18" customHeight="1"/>
-    <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>Best combination (MAX)</t>
-        </is>
-      </c>
-      <c r="C14" s="9">
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>Best revenue (MAX)</t>
+        </is>
+      </c>
+      <c r="B12" s="9">
         <f>MAX(C8:E10)</f>
         <v/>
       </c>
-      <c r="D14" s="10">
-        <f>_xlfn.FORMULATEXT(C14)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="18" customHeight="1"/>
-    <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="11" t="inlineStr">
-        <is>
-          <t>$1,028 -- barley at No. 1. Lock every reference instead and all nine cells read $585, the canola No. 1 figure, because nothing moves when you fill.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="18" customHeight="1"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>Best combination</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>Barley at No. 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>Formula: =$B8*$B$4*C$7, filled across and down. The yield $B8 has an absolute column and a relative row, so it stays in column B while moving down the crops. The factor C$7 has a relative column and an absolute row, so it moves across the grades while staying on row 7. The base price $B$4 is absolute in both, because it never changes.</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="n"/>
+      <c r="C15" s="11" t="n"/>
+      <c r="D15" s="11" t="n"/>
+      <c r="E15" s="11" t="n"/>
+      <c r="F15" s="11" t="n"/>
+      <c r="G15" s="11" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="11" t="n"/>
+      <c r="B16" s="11" t="n"/>
+      <c r="C16" s="11" t="n"/>
+      <c r="D16" s="11" t="n"/>
+      <c r="E16" s="11" t="n"/>
+      <c r="F16" s="11" t="n"/>
+      <c r="G16" s="11" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="11" t="n"/>
+      <c r="B17" s="11" t="n"/>
+      <c r="C17" s="11" t="n"/>
+      <c r="D17" s="11" t="n"/>
+      <c r="E17" s="11" t="n"/>
+      <c r="F17" s="11" t="n"/>
+      <c r="G17" s="11" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="11" t="n"/>
+      <c r="B18" s="11" t="n"/>
+      <c r="C18" s="11" t="n"/>
+      <c r="D18" s="11" t="n"/>
+      <c r="E18" s="11" t="n"/>
+      <c r="F18" s="11" t="n"/>
+      <c r="G18" s="11" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>The grid is formatted as currency with no decimals ($#,##0).</t>
+        </is>
+      </c>
+      <c r="B20" s="13" t="n"/>
+      <c r="C20" s="13" t="n"/>
+      <c r="D20" s="13" t="n"/>
+      <c r="E20" s="13" t="n"/>
+      <c r="F20" s="13" t="n"/>
+      <c r="G20" s="13" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="14" t="inlineStr">
+        <is>
+          <t>With every reference locked, nothing moves when the formula is filled -- all nine cells show the same number, $585, canola at No. 1.</t>
+        </is>
+      </c>
+      <c r="B22" s="15" t="n"/>
+      <c r="C22" s="15" t="n"/>
+      <c r="D22" s="15" t="n"/>
+      <c r="E22" s="15" t="n"/>
+      <c r="F22" s="15" t="n"/>
+      <c r="G22" s="15" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="15" t="n"/>
+      <c r="B23" s="15" t="n"/>
+      <c r="C23" s="15" t="n"/>
+      <c r="D23" s="15" t="n"/>
+      <c r="E23" s="15" t="n"/>
+      <c r="F23" s="15" t="n"/>
+      <c r="G23" s="15" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="16" t="inlineStr">
+        <is>
+          <t>Part (a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="11" t="inlineStr">
+        <is>
+          <t>Part (b)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="13" t="inlineStr">
+        <is>
+          <t>Part (c)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>Part (d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="15" t="inlineStr">
+        <is>
+          <t>Part (e)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A16:E16"/>
-    <mergeCell ref="A2:F2"/>
+  <mergeCells count="3">
+    <mergeCell ref="A20:G20"/>
+    <mergeCell ref="A15:G18"/>
+    <mergeCell ref="A22:G23"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
